--- a/outputs/Payroll_Summary_2026-02.xlsx
+++ b/outputs/Payroll_Summary_2026-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,50 +436,70 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>全名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>工時</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>OT工時</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>底薪</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>總佣金</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>津貼</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>報銷</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>微調</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>出勤獎</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>總收入</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MPF扣除</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MPF狀態</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>實發薪資</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>地點</t>
         </is>
@@ -491,17 +511,19 @@
           <t>Chau</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yim Wan Chau</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -512,15 +534,27 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>180</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>180</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>開會</t>
         </is>
@@ -532,36 +566,50 @@
           <t>Connie</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chu Pik Fung</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>59</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>3540</v>
+      </c>
+      <c r="F3" t="n">
         <v>315.71</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
-        <v>315.71</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315.71</v>
-      </c>
-      <c r="K3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3855.71</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3855.71</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Tuen Wan Aeon</t>
         </is>
@@ -573,36 +621,50 @@
           <t>Irene</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chan Yun Hing</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>128</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>7680</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2779.17</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>10459.17</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>10459.17</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>SW Wing On</t>
         </is>
@@ -614,36 +676,50 @@
           <t>Joe</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>75.5</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wong Sui Ping</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>-4.5</v>
+        <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>4260</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
+        <v>4830</v>
+      </c>
+      <c r="F5" t="n">
         <v>1711.52</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
-        <v>6034.52</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>6034.52</v>
-      </c>
-      <c r="K5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6604.52</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>6604.52</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Tai Po Yata</t>
         </is>
@@ -655,36 +731,50 @@
           <t>Ling</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>123.58</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lok Yin Ling</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>3.58</v>
+        <v>120</v>
       </c>
       <c r="D6" t="n">
-        <v>6994.17</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>6655</v>
+      </c>
+      <c r="F6" t="n">
         <v>1500.59</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
-        <v>8494.75</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8494.75</v>
-      </c>
-      <c r="K6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8155.59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>8155.59</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Yuen Long Citistore</t>
         </is>
@@ -696,36 +786,50 @@
           <t>Mei Kiu</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Leung Mei Kiu</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>48</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>3120</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>473.14</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3593.14</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>3593.14</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Tuen Wan Yata</t>
         </is>
@@ -737,36 +841,50 @@
           <t>Wah</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>121.5</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lo Chun Wah</t>
+        </is>
       </c>
       <c r="C8" t="n">
+        <v>120</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>7380</v>
-      </c>
       <c r="E8" t="n">
+        <v>7290</v>
+      </c>
+      <c r="F8" t="n">
         <v>3274.29</v>
       </c>
-      <c r="F8" t="n">
-        <v>450</v>
-      </c>
       <c r="G8" t="n">
-        <v>11104.29</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11104.29</v>
-      </c>
-      <c r="K8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10564.29</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>10564.29</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Kowloon Bay Fortress</t>
         </is>
@@ -778,36 +896,50 @@
           <t>Wu Sir</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Woo Kin Ming</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>59</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>3835</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2650.35</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>6485.35</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>豁免期</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🚫 永久豁免 (非 MPF 員工)</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>6485.35</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Kwai Fong Fortress</t>
         </is>

--- a/outputs/Payroll_Summary_2026-02.xlsx
+++ b/outputs/Payroll_Summary_2026-02.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>員工</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>全名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>工時</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OT工時</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>底薪</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>總佣金</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>津貼</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>報銷</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>微調</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>出勤獎</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>總收入</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MPF扣除</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MPF狀態</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>實發薪資</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>地點</t>
         </is>
@@ -685,10 +673,10 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>-4.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4830</v>
+        <v>4530</v>
       </c>
       <c r="F5" t="n">
         <v>1711.52</v>
@@ -706,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6604.52</v>
+        <v>6304.52</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -717,7 +705,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6604.52</v>
+        <v>6304.52</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -798,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3120</v>
+        <v>2880</v>
       </c>
       <c r="F7" t="n">
         <v>473.14</v>
@@ -816,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3593.14</v>
+        <v>3353.14</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -827,7 +815,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3593.14</v>
+        <v>3353.14</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
